--- a/Data/EC/NIT-9020024541.xlsx
+++ b/Data/EC/NIT-9020024541.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EACD7B1F-9974-4FA0-A899-DBA7B990329A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{619A5FBF-D96D-4225-89FE-344E4041D484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9F8E14C8-4874-4774-899E-194D0F8C09C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{08447F29-2E6D-41D1-9F9F-9D479350A3D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="50">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -74,6 +74,9 @@
     <t>HENRY ANTONIO SALAS ACOSTA</t>
   </si>
   <si>
+    <t>2607</t>
+  </si>
+  <si>
     <t>2606</t>
   </si>
   <si>
@@ -83,21 +86,33 @@
     <t>2604</t>
   </si>
   <si>
+    <t>2603</t>
+  </si>
+  <si>
     <t>8981273</t>
   </si>
   <si>
     <t>OSCAR ENRIQUE ANILLO GOMEZ</t>
   </si>
   <si>
-    <t>2603</t>
-  </si>
-  <si>
     <t>1002249882</t>
   </si>
   <si>
     <t>ANGEL DE JESUS VILLADIEGO HERNANDEZ</t>
   </si>
   <si>
+    <t>34998916</t>
+  </si>
+  <si>
+    <t>JAIDYS ANTONIA MAUSSA MONTES</t>
+  </si>
+  <si>
+    <t>1051450275</t>
+  </si>
+  <si>
+    <t>JHON JAIRO BABILONIA PEREZ</t>
+  </si>
+  <si>
     <t>1052079189</t>
   </si>
   <si>
@@ -107,10 +122,22 @@
     <t>2602</t>
   </si>
   <si>
-    <t>1047481401</t>
-  </si>
-  <si>
-    <t>ALDAIR ANTONIO ROMERO PUELLO</t>
+    <t>1103101092</t>
+  </si>
+  <si>
+    <t>CESAR ANDRES ARRIETA ASCENCIO</t>
+  </si>
+  <si>
+    <t>1047518206</t>
+  </si>
+  <si>
+    <t>EDULAY RAMOS GARCES</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
   </si>
   <si>
     <t>1007946217</t>
@@ -123,6 +150,12 @@
   </si>
   <si>
     <t>JULIETH PAOLA RENTERIA MAZA</t>
+  </si>
+  <si>
+    <t>1047447645</t>
+  </si>
+  <si>
+    <t>CRISTINA DE JESUS CASTILLO VILLAREAL</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -521,22 +554,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0587661-9D6C-940E-ED21-8763F8E615EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4FF517-35C4-9910-837D-CCBE82A2B997}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -545,7 +578,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -558,7 +591,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -887,27 +920,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DD655F-23C8-4B9A-AFE5-6B87C4254DA3}">
-  <dimension ref="B2:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920FB51F-77A3-4A3B-BC3C-4374618B338A}">
+  <dimension ref="B2:J58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -916,7 +949,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -927,7 +960,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -938,7 +971,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -949,10 +982,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -965,8 +998,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -981,15 +1014,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1614558</v>
+        <v>2453289</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -997,27 +1030,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F13" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1037,16 +1070,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1069,7 +1102,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1092,7 +1125,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1115,21 +1148,21 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>16</v>
-      </c>
       <c r="F19" s="18">
-        <v>19200</v>
+        <v>96000</v>
       </c>
       <c r="G19" s="18">
         <v>2400000</v>
@@ -1138,64 +1171,64 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>70037</v>
+        <v>12800</v>
       </c>
       <c r="G20" s="18">
-        <v>1750905</v>
+        <v>2400000</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>18</v>
-      </c>
       <c r="E21" s="16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21" s="18">
-        <v>70037</v>
+        <v>19200</v>
       </c>
       <c r="G21" s="18">
-        <v>1750905</v>
+        <v>2400000</v>
       </c>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F22" s="18">
         <v>70037</v>
@@ -1207,21 +1240,21 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F23" s="18">
-        <v>30349</v>
+        <v>70037</v>
       </c>
       <c r="G23" s="18">
         <v>1750905</v>
@@ -1230,18 +1263,18 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>20</v>
-      </c>
       <c r="E24" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F24" s="18">
         <v>70037</v>
@@ -1253,18 +1286,18 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>20</v>
-      </c>
       <c r="E25" s="16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" s="18">
         <v>70037</v>
@@ -1276,21 +1309,21 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>20</v>
-      </c>
       <c r="E26" s="16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26" s="18">
-        <v>70037</v>
+        <v>30349</v>
       </c>
       <c r="G26" s="18">
         <v>1750905</v>
@@ -1299,44 +1332,44 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F27" s="18">
-        <v>70037</v>
+        <v>80000</v>
       </c>
       <c r="G27" s="18">
-        <v>1750905</v>
+        <v>2000000</v>
       </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F28" s="18">
-        <v>32684</v>
+        <v>70037</v>
       </c>
       <c r="G28" s="18">
         <v>1750905</v>
@@ -1345,7 +1378,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1356,7 +1389,7 @@
         <v>23</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" s="18">
         <v>70037</v>
@@ -1368,21 +1401,21 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" s="18">
-        <v>44357</v>
+        <v>70037</v>
       </c>
       <c r="G30" s="18">
         <v>1750905</v>
@@ -1391,7 +1424,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1402,7 +1435,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" s="18">
         <v>70037</v>
@@ -1414,7 +1447,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1425,7 +1458,7 @@
         <v>25</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="18">
         <v>70037</v>
@@ -1437,7 +1470,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1481,7 @@
         <v>25</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="18">
         <v>70037</v>
@@ -1460,7 +1493,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1504,7 @@
         <v>25</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F34" s="18">
         <v>70037</v>
@@ -1483,7 +1516,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1494,10 +1527,10 @@
         <v>25</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F35" s="18">
-        <v>39688</v>
+        <v>32684</v>
       </c>
       <c r="G35" s="18">
         <v>1750905</v>
@@ -1506,64 +1539,64 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="18">
-        <v>70037</v>
+        <v>74000</v>
       </c>
       <c r="G36" s="18">
-        <v>1750905</v>
+        <v>1850000</v>
       </c>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="18">
-        <v>70037</v>
+        <v>74000</v>
       </c>
       <c r="G37" s="18">
-        <v>1750905</v>
+        <v>1850000</v>
       </c>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F38" s="18">
         <v>70037</v>
@@ -1575,18 +1608,18 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F39" s="18">
         <v>70037</v>
@@ -1598,57 +1631,333 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B40" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="22" t="s">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G40" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G41" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G42" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G43" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G44" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="24">
+      <c r="F45" s="18">
         <v>39688</v>
       </c>
-      <c r="G40" s="24">
-        <v>1750905</v>
-      </c>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B45" s="32" t="s">
+      <c r="G45" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G46" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="20"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G47" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G48" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G49" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G50" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="18">
+        <v>39688</v>
+      </c>
+      <c r="G51" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="32"/>
-      <c r="H45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B46" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="H46" s="1" t="s">
+      <c r="D52" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="E52" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="24">
+        <v>56029</v>
+      </c>
+      <c r="G52" s="24">
+        <v>1750905</v>
+      </c>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="26"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="32"/>
+      <c r="H57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="32"/>
+      <c r="H58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H57:J57"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
